--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487496_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487496_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9231</v>
+        <v>5.4812</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1761</v>
+        <v>3.4402</v>
       </c>
       <c r="F2" t="n">
-        <v>1.747</v>
+        <v>2.041</v>
       </c>
       <c r="G2" t="n">
         <v>6.0902</v>
@@ -610,13 +610,13 @@
         <v>2.1543</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2615</v>
+        <v>0.2966</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3276</v>
+        <v>-0.0635</v>
       </c>
       <c r="U2" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.3601</v>
       </c>
       <c r="V2" t="n">
         <v>-1.1014</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9042</v>
+        <v>3.515</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7842</v>
+        <v>2.6623</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1201</v>
+        <v>0.8528</v>
       </c>
       <c r="G3" t="n">
         <v>1.7524</v>
@@ -688,13 +688,13 @@
         <v>2.546</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.2986</v>
+        <v>-0.6878</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.331</v>
+        <v>-0.4529</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0324</v>
+        <v>-0.2349</v>
       </c>
       <c r="V3" t="n">
         <v>0.8837</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9298999999999999</v>
+        <v>2.3496</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2534</v>
+        <v>0.8723</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1833</v>
+        <v>1.4773</v>
       </c>
       <c r="G4" t="n">
         <v>-0.0756</v>
@@ -766,13 +766,13 @@
         <v>2.7419</v>
       </c>
       <c r="S4" t="n">
-        <v>-2.4865</v>
+        <v>-1.0667</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.5686</v>
+        <v>-0.4429</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9179</v>
+        <v>-0.6239</v>
       </c>
       <c r="V4" t="n">
         <v>2.7086</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8176</v>
+        <v>1.2947</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8593</v>
+        <v>0.0188</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6769</v>
+        <v>1.2759</v>
       </c>
       <c r="G5" t="n">
         <v>1.442</v>
@@ -844,13 +844,13 @@
         <v>1.3709</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7408</v>
+        <v>-0.2636</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0339</v>
+        <v>-0.1559</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2932</v>
+        <v>-0.1078</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2754</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. KOUROUMA</t>
+          <t>J. BUENO DE LA ROSA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2787</v>
+        <v>-0.0083</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6855</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4068</v>
+        <v>-0.0083</v>
       </c>
       <c r="G6" t="n">
-        <v>0.837</v>
+        <v>-0.0677</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7962</v>
+        <v>-0.0677</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0408</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.361</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1993</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1617</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.524</v>
+        <v>-0.0677</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4031</v>
+        <v>-0.0677</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1209</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3917</v>
+        <v>0.1958</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5668</v>
+        <v>0.1958</v>
       </c>
       <c r="S6" t="n">
-        <v>2.9901</v>
+        <v>-0.1364</v>
       </c>
       <c r="T6" t="n">
-        <v>2.6148</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3753</v>
+        <v>-0.1364</v>
       </c>
       <c r="V6" t="n">
-        <v>-3.1567</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-1.3318</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.8249</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ROA RODRIGUEZ</t>
+          <t>I. OLALQUIAGA BAZO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,37 +955,37 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2507</v>
+        <v>-0.3109</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2716</v>
+        <v>-0.8604000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0209</v>
+        <v>0.5495</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0166</v>
+        <v>0.0687</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9766</v>
+        <v>0.4781</v>
       </c>
       <c r="I7" t="n">
-        <v>0.96</v>
+        <v>-0.4093</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3593</v>
+        <v>-0.6822</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.0464</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6871</v>
+        <v>-0.6822</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3427</v>
+        <v>0.751</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0698</v>
+        <v>0.4781</v>
       </c>
       <c r="O7" t="n">
         <v>0.2729</v>
@@ -1000,28 +1000,28 @@
         <v>0.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>1.643</v>
+        <v>-0.7713</v>
       </c>
       <c r="T7" t="n">
-        <v>1.6309</v>
+        <v>-0.1782</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0121</v>
+        <v>-0.5931</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.7673</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.7673</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. BUENO DE LA ROSA</t>
+          <t>A. ROA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0083</v>
+        <v>-0.7413</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.1459</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0083</v>
+        <v>-0.8872</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0677</v>
+        <v>-0.0166</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0677</v>
+        <v>-0.9766</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-0.3593</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>-1.0464</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.6871</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0677</v>
+        <v>0.3427</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0677</v>
+        <v>0.0698</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.2729</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1958</v>
+        <v>0.3917</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1958</v>
+        <v>0.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1364</v>
+        <v>0.6509</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.5052</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1364</v>
+        <v>0.1457</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.7673</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.7673</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. OLALQUIAGA BAZO</t>
+          <t>R. CHOITHRAMANI BLANCO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3644</v>
+        <v>-1.0074</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8604000000000001</v>
+        <v>-3.7437</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4961</v>
+        <v>2.7364</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0687</v>
+        <v>-0.7156</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4781</v>
+        <v>0.967</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4093</v>
+        <v>-1.6826</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6822</v>
+        <v>-0.1999</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1.6399</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6822</v>
+        <v>-1.8398</v>
       </c>
       <c r="M9" t="n">
-        <v>0.751</v>
+        <v>-0.5157</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4781</v>
+        <v>-0.6729000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2729</v>
+        <v>0.1572</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3917</v>
+        <v>-2.3502</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-4.8962</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3917</v>
+        <v>2.546</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8248</v>
+        <v>0.5089</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1782</v>
+        <v>0.1359</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6466</v>
+        <v>0.373</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.5495</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.3329</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. CHOITHRAMANI BLANCO</t>
+          <t>O. KOUROUMA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0354</v>
+        <v>-1.6864</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.9054</v>
+        <v>-1.1994</v>
       </c>
       <c r="F10" t="n">
-        <v>2.87</v>
+        <v>-0.487</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7156</v>
+        <v>0.837</v>
       </c>
       <c r="H10" t="n">
-        <v>0.967</v>
+        <v>0.7962</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.6826</v>
+        <v>0.0408</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1999</v>
+        <v>1.361</v>
       </c>
       <c r="K10" t="n">
-        <v>1.6399</v>
+        <v>1.1993</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.8398</v>
+        <v>0.1617</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5157</v>
+        <v>-0.524</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.4031</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1572</v>
+        <v>-0.1209</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.3502</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.8962</v>
+        <v>-1.9585</v>
       </c>
       <c r="R10" t="n">
-        <v>2.546</v>
+        <v>1.5668</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4808</v>
+        <v>1.025</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0259</v>
+        <v>0.7299</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5067</v>
+        <v>0.2951</v>
       </c>
       <c r="V10" t="n">
-        <v>1.5495</v>
+        <v>-3.1567</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2166</v>
+        <v>-1.3318</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3329</v>
+        <v>-1.8249</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3532</v>
+        <v>-4.2463</v>
       </c>
       <c r="E11" t="n">
         <v>-3.0061</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3471</v>
+        <v>-1.2402</v>
       </c>
       <c r="G11" t="n">
         <v>-1.2318</v>
@@ -1312,13 +1312,13 @@
         <v>0.7834</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.709</v>
+        <v>-1.6021</v>
       </c>
       <c r="T11" t="n">
         <v>-0.7128</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.9962</v>
+        <v>-0.8893</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2166</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.342900000000001</v>
+        <v>4.639899999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.9672</v>
+        <v>-1.6701</v>
       </c>
       <c r="F12" t="n">
-        <v>6.3103</v>
+        <v>6.3102</v>
       </c>
       <c r="G12" t="n">
         <v>8.083</v>
@@ -1363,7 +1363,7 @@
         <v>7.400899999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>5.880599999999999</v>
+        <v>5.8806</v>
       </c>
       <c r="K12" t="n">
         <v>1.3125</v>
@@ -1381,7 +1381,7 @@
         <v>2.8328</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9791999999999998</v>
+        <v>0.9792000000000001</v>
       </c>
       <c r="Q12" t="n">
         <v>-13.7093</v>
@@ -1390,13 +1390,13 @@
         <v>14.6885</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.3437</v>
+        <v>-2.0465</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9323000000000009</v>
+        <v>-0.6352</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.4113</v>
+        <v>-1.4115</v>
       </c>
       <c r="V12" t="n">
         <v>-2.375599999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.98</v>
+        <v>4.602</v>
       </c>
       <c r="E13" t="n">
-        <v>4.1361</v>
+        <v>3.6244</v>
       </c>
       <c r="F13" t="n">
-        <v>0.844</v>
+        <v>0.9776</v>
       </c>
       <c r="G13" t="n">
         <v>0.0575</v>
@@ -1468,13 +1468,13 @@
         <v>1.7626</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8484</v>
+        <v>0.4704</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6516</v>
+        <v>0.14</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1967</v>
+        <v>0.3304</v>
       </c>
       <c r="V13" t="n">
         <v>2.3115</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.8575</v>
+        <v>2.3247</v>
       </c>
       <c r="E14" t="n">
-        <v>1.343</v>
+        <v>0.8313</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5146</v>
+        <v>1.4934</v>
       </c>
       <c r="G14" t="n">
         <v>0.7628</v>
@@ -1546,13 +1546,13 @@
         <v>1.3709</v>
       </c>
       <c r="S14" t="n">
-        <v>1.9583</v>
+        <v>1.4255</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1669</v>
+        <v>0.6552</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7915</v>
+        <v>0.7703</v>
       </c>
       <c r="V14" t="n">
         <v>1.7032</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5407999999999999</v>
+        <v>0.8091</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4844</v>
+        <v>-0.3821</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0252</v>
+        <v>1.1912</v>
       </c>
       <c r="G15" t="n">
         <v>-0.6818</v>
@@ -1624,13 +1624,13 @@
         <v>0.9792</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2434</v>
+        <v>0.5117</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2182</v>
+        <v>0.3205</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0252</v>
+        <v>0.1911</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4059</v>
+        <v>0.7304</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.1371</v>
+        <v>-0.6254</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5429</v>
+        <v>1.3558</v>
       </c>
       <c r="G16" t="n">
         <v>1.0699</v>
@@ -1702,13 +1702,13 @@
         <v>1.5668</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2724</v>
+        <v>0.0522</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7128</v>
+        <v>-0.2011</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4405</v>
+        <v>0.2533</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0581</v>
+        <v>0.1672</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2574</v>
+        <v>0.5613</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8007</v>
+        <v>-0.3941</v>
       </c>
       <c r="G17" t="n">
         <v>-1.5358</v>
@@ -1780,13 +1780,13 @@
         <v>1.3709</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0089</v>
+        <v>0.2163</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7611</v>
+        <v>0.0576</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2479</v>
+        <v>0.1587</v>
       </c>
       <c r="V17" t="n">
         <v>1.0949</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. SAMA PEREZ</t>
+          <t>J. ARGENTI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4968</v>
+        <v>-0.9357</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6966</v>
+        <v>-1.0913</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8003</v>
+        <v>0.1556</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.1934</v>
+        <v>0.4954</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.3254</v>
+        <v>0.9550999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>1.132</v>
+        <v>-0.4598</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.0121</v>
+        <v>0.9496</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.5827</v>
+        <v>0.3385</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5706</v>
+        <v>0.611</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1813</v>
+        <v>-0.4542</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7427</v>
+        <v>0.6166</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5614</v>
+        <v>-1.0708</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.7626</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9377</v>
+        <v>-1.9585</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1751</v>
+        <v>1.3709</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1476</v>
+        <v>0.0401</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6034</v>
+        <v>-0.0823</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4558</v>
+        <v>0.1225</v>
       </c>
       <c r="V18" t="n">
-        <v>2.3115</v>
+        <v>-0.8837</v>
       </c>
       <c r="W18" t="n">
-        <v>3.6498</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.3383</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. ARGENTI</t>
+          <t>I. SAMA PEREZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6345</v>
+        <v>-1.1613</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6029</v>
+        <v>-0.9012</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0316</v>
+        <v>-0.2601</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4954</v>
+        <v>-2.1934</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9550999999999999</v>
+        <v>-3.3254</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4598</v>
+        <v>1.132</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9496</v>
+        <v>-2.0121</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3385</v>
+        <v>-2.5827</v>
       </c>
       <c r="L19" t="n">
-        <v>0.611</v>
+        <v>0.5706</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4542</v>
+        <v>-0.1813</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6166</v>
+        <v>-0.7427</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0708</v>
+        <v>0.5614</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.5875</v>
+        <v>-1.7626</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9585</v>
+        <v>-2.9377</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3709</v>
+        <v>1.1751</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6587</v>
+        <v>0.4832</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.594</v>
+        <v>0.3987</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0646</v>
+        <v>0.0844</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.8837</v>
+        <v>2.3115</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>3.6498</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.8837</v>
+        <v>-1.3383</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.468</v>
+        <v>-2.6505</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.4683</v>
+        <v>-2.5706</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0003</v>
+        <v>-0.0799</v>
       </c>
       <c r="G20" t="n">
         <v>-1.8255</v>
@@ -2014,13 +2014,13 @@
         <v>1.9585</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1071</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2682</v>
+        <v>-0.3705</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3753</v>
+        <v>0.2951</v>
       </c>
       <c r="V20" t="n">
         <v>-1.7288</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.4697</v>
+        <v>-6.8643</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.1425</v>
+        <v>-5.7565</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3272</v>
+        <v>-1.1078</v>
       </c>
       <c r="G21" t="n">
         <v>-4.232</v>
@@ -2092,13 +2092,13 @@
         <v>2.1543</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9789</v>
+        <v>0.5843</v>
       </c>
       <c r="T21" t="n">
-        <v>1.1074</v>
+        <v>0.4934</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1286</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>-2.4332</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.342899999999999</v>
+        <v>-2.978399999999999</v>
       </c>
       <c r="E22" t="n">
         <v>-6.3101</v>
       </c>
       <c r="F22" t="n">
-        <v>1.967200000000001</v>
+        <v>3.3317</v>
       </c>
       <c r="G22" t="n">
         <v>-8.0829</v>
@@ -2170,13 +2170,13 @@
         <v>13.7092</v>
       </c>
       <c r="S22" t="n">
-        <v>2.3437</v>
+        <v>3.7083</v>
       </c>
       <c r="T22" t="n">
-        <v>1.4114</v>
+        <v>1.4115</v>
       </c>
       <c r="U22" t="n">
-        <v>0.9322999999999999</v>
+        <v>2.2967</v>
       </c>
       <c r="V22" t="n">
         <v>2.3754</v>
